--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_15.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:M133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4625 +469,5970 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:51.851</t>
+          <t>2026-05-29 09:41:13.187</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421973181</v>
+        <v>1780022471623</v>
       </c>
       <c r="C2" t="n">
-        <v>88000</v>
+        <v>89723</v>
       </c>
       <c r="D2" t="n">
-        <v>984.9299999999999</v>
+        <v>4849.89</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>684</v>
+        <v>360</v>
       </c>
       <c r="G2" t="n">
-        <v>65.48999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="L2" t="n">
+        <v>122</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:51.852</t>
+          <t>2026-05-29 09:41:13.188</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421973382</v>
+        <v>1780022471823</v>
       </c>
       <c r="C3" t="n">
-        <v>87143</v>
+        <v>89684</v>
       </c>
       <c r="D3" t="n">
-        <v>78.68000000000001</v>
+        <v>4568.39</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>360</v>
       </c>
       <c r="G3" t="n">
-        <v>65.48999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L3" t="n">
+        <v>103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:51.852</t>
+          <t>2026-05-29 09:41:13.189</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421973584</v>
+        <v>1780022472023</v>
       </c>
       <c r="C4" t="n">
-        <v>87366</v>
+        <v>89419</v>
       </c>
       <c r="D4" t="n">
-        <v>297.75</v>
+        <v>4074.97</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>684</v>
+        <v>360</v>
       </c>
       <c r="G4" t="n">
-        <v>65.48999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L4" t="n">
+        <v>105</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:51.888</t>
+          <t>2026-05-29 09:41:13.190</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421973785</v>
+        <v>1780022472223</v>
       </c>
       <c r="C5" t="n">
-        <v>87571</v>
+        <v>90416</v>
       </c>
       <c r="D5" t="n">
-        <v>487.86</v>
+        <v>4868.22</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>684</v>
+        <v>360</v>
       </c>
       <c r="G5" t="n">
-        <v>65.48999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>966</v>
+      </c>
+      <c r="L5" t="n">
+        <v>106</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:51.889</t>
+          <t>2026-05-29 09:41:14.938</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421973987</v>
+        <v>1780022472423</v>
       </c>
       <c r="C6" t="n">
-        <v>87844</v>
+        <v>87518</v>
       </c>
       <c r="D6" t="n">
-        <v>736.47</v>
+        <v>1726.81</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>846</v>
+        <v>360</v>
       </c>
       <c r="G6" t="n">
-        <v>76.81999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2514</v>
+      </c>
+      <c r="L6" t="n">
+        <v>104</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:52.506</t>
+          <t>2026-05-29 09:41:14.940</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421974188</v>
+        <v>1780022472623</v>
       </c>
       <c r="C7" t="n">
-        <v>86959</v>
+        <v>86703</v>
       </c>
       <c r="D7" t="n">
-        <v>-185.35</v>
+        <v>825.47</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
-        <v>846</v>
+        <v>360</v>
       </c>
       <c r="G7" t="n">
-        <v>76.81999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2315</v>
+      </c>
+      <c r="L7" t="n">
+        <v>112</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:52.507</t>
+          <t>2026-05-29 09:41:14.941</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421974390</v>
+        <v>1780022472823</v>
       </c>
       <c r="C8" t="n">
-        <v>87378</v>
+        <v>86104</v>
       </c>
       <c r="D8" t="n">
-        <v>242.91</v>
+        <v>185.2</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>846</v>
+        <v>360</v>
       </c>
       <c r="G8" t="n">
-        <v>76.81999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2117</v>
+      </c>
+      <c r="L8" t="n">
+        <v>105</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:52.508</t>
+          <t>2026-05-29 09:41:14.943</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421974591</v>
+        <v>1780022473042</v>
       </c>
       <c r="C9" t="n">
-        <v>87651</v>
+        <v>86463</v>
       </c>
       <c r="D9" t="n">
-        <v>503.77</v>
+        <v>534.9400000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
-        <v>846</v>
+        <v>360</v>
       </c>
       <c r="G9" t="n">
-        <v>76.81999999999999</v>
+        <v>315.76</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="L9" t="n">
+        <v>108</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:52.508</t>
+          <t>2026-05-29 09:41:14.945</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421974792</v>
+        <v>1780022473242</v>
       </c>
       <c r="C10" t="n">
-        <v>87823</v>
+        <v>86470</v>
       </c>
       <c r="D10" t="n">
-        <v>650.58</v>
+        <v>515.1900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="G10" t="n">
-        <v>77.92</v>
+        <v>315.76</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1702</v>
+      </c>
+      <c r="L10" t="n">
+        <v>108</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.248</t>
+          <t>2026-05-29 09:41:14.996</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421974994</v>
+        <v>1780022473442</v>
       </c>
       <c r="C11" t="n">
-        <v>87030</v>
+        <v>86554</v>
       </c>
       <c r="D11" t="n">
-        <v>-174.95</v>
+        <v>573.4299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="G11" t="n">
-        <v>77.92</v>
+        <v>315.76</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1553</v>
+      </c>
+      <c r="L11" t="n">
+        <v>112</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.250</t>
+          <t>2026-05-29 09:41:14.997</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421975195</v>
+        <v>1780022473642</v>
       </c>
       <c r="C12" t="n">
-        <v>87306</v>
+        <v>86640</v>
       </c>
       <c r="D12" t="n">
-        <v>109.8</v>
+        <v>630.76</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="G12" t="n">
-        <v>77.92</v>
+        <v>315.76</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1354</v>
+      </c>
+      <c r="L12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.276</t>
+          <t>2026-05-29 09:41:14.998</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421975397</v>
+        <v>1780022473842</v>
       </c>
       <c r="C13" t="n">
-        <v>87617</v>
+        <v>86093</v>
       </c>
       <c r="D13" t="n">
-        <v>415.31</v>
+        <v>52.22</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="G13" t="n">
-        <v>77.92</v>
+        <v>315.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L13" t="n">
+        <v>115</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.864</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.531</t>
+          <t>2026-05-29 09:41:15.005</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421975598</v>
+        <v>1780022474042</v>
       </c>
       <c r="C14" t="n">
-        <v>86931</v>
+        <v>85628</v>
       </c>
       <c r="D14" t="n">
-        <v>-291.46</v>
+        <v>-415.39</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>806</v>
+        <v>360</v>
       </c>
       <c r="G14" t="n">
-        <v>63.59</v>
+        <v>315.76</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>963</v>
+      </c>
+      <c r="L14" t="n">
+        <v>116</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.586</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.538</t>
+          <t>2026-05-29 09:41:15.267</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421975799</v>
+        <v>1780022474242</v>
       </c>
       <c r="C15" t="n">
-        <v>87251</v>
+        <v>85585</v>
       </c>
       <c r="D15" t="n">
-        <v>43.12</v>
+        <v>-437.62</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>806</v>
+        <v>360</v>
       </c>
       <c r="G15" t="n">
-        <v>63.59</v>
+        <v>315.76</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1025</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.954</t>
+          <t>2026-05-29 09:41:15.268</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421976001</v>
+        <v>1780022474461</v>
       </c>
       <c r="C16" t="n">
-        <v>87557</v>
+        <v>85452</v>
       </c>
       <c r="D16" t="n">
-        <v>346.96</v>
+        <v>-548.74</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>806</v>
+        <v>360</v>
       </c>
       <c r="G16" t="n">
-        <v>63.59</v>
+        <v>315.76</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>807</v>
+      </c>
+      <c r="L16" t="n">
+        <v>114</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:53.955</t>
+          <t>2026-05-29 09:41:15.707</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421976202</v>
+        <v>1780022474661</v>
       </c>
       <c r="C17" t="n">
-        <v>87887</v>
+        <v>86484</v>
       </c>
       <c r="D17" t="n">
-        <v>659.61</v>
+        <v>510.7</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>644</v>
+        <v>360</v>
       </c>
       <c r="G17" t="n">
-        <v>71.41</v>
+        <v>315.76</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L17" t="n">
+        <v>113</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:54.355</t>
+          <t>2026-05-29 09:41:15.708</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421976404</v>
+        <v>1780022474861</v>
       </c>
       <c r="C18" t="n">
-        <v>87026</v>
+        <v>85323</v>
       </c>
       <c r="D18" t="n">
-        <v>-234.37</v>
+        <v>-675.84</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>644</v>
+        <v>4197</v>
       </c>
       <c r="G18" t="n">
-        <v>71.41</v>
+        <v>315.76</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>846</v>
+      </c>
+      <c r="L18" t="n">
+        <v>107</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:54.356</t>
+          <t>2026-05-29 09:41:16.307</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421976605</v>
+        <v>1780022475061</v>
       </c>
       <c r="C19" t="n">
-        <v>87357</v>
+        <v>85319</v>
       </c>
       <c r="D19" t="n">
-        <v>108.35</v>
+        <v>-646.04</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>644</v>
+        <v>4197</v>
       </c>
       <c r="G19" t="n">
-        <v>71.41</v>
+        <v>315.76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L19" t="n">
+        <v>119</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.931</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:54.961</t>
+          <t>2026-05-29 09:41:16.308</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421976806</v>
+        <v>1780022475261</v>
       </c>
       <c r="C20" t="n">
-        <v>87671</v>
+        <v>85221</v>
       </c>
       <c r="D20" t="n">
-        <v>416.93</v>
+        <v>-711.74</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G20" t="n">
-        <v>66.36</v>
+        <v>315.76</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1047</v>
+      </c>
+      <c r="L20" t="n">
+        <v>107</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.761</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:54.961</t>
+          <t>2026-05-29 09:41:17.010</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421977008</v>
+        <v>1780022475461</v>
       </c>
       <c r="C21" t="n">
-        <v>87144</v>
+        <v>85211</v>
       </c>
       <c r="D21" t="n">
-        <v>-130.91</v>
+        <v>-686.15</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G21" t="n">
-        <v>66.36</v>
+        <v>315.76</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1549</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.517</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:54.962</t>
+          <t>2026-05-29 09:41:17.011</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421977209</v>
+        <v>1780022475661</v>
       </c>
       <c r="C22" t="n">
-        <v>87181</v>
+        <v>84134</v>
       </c>
       <c r="D22" t="n">
-        <v>-87.37</v>
+        <v>-1728.85</v>
       </c>
       <c r="E22" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F22" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G22" t="n">
-        <v>66.36</v>
+        <v>315.76</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L22" t="n">
+        <v>112</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.649</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:55.379</t>
+          <t>2026-05-29 09:41:17.013</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421977411</v>
+        <v>1780022475861</v>
       </c>
       <c r="C23" t="n">
-        <v>87379</v>
+        <v>84901</v>
       </c>
       <c r="D23" t="n">
-        <v>115</v>
+        <v>-875.4</v>
       </c>
       <c r="E23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G23" t="n">
-        <v>66.36</v>
+        <v>315.76</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L23" t="n">
+        <v>117</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.801</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:55.411</t>
+          <t>2026-05-29 09:41:17.015</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421977612</v>
+        <v>1780022476061</v>
       </c>
       <c r="C24" t="n">
-        <v>87641</v>
+        <v>85098</v>
       </c>
       <c r="D24" t="n">
-        <v>371.25</v>
+        <v>-634.63</v>
       </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F24" t="n">
-        <v>746</v>
+        <v>4197</v>
       </c>
       <c r="G24" t="n">
-        <v>63.09</v>
+        <v>315.76</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>952</v>
+      </c>
+      <c r="L24" t="n">
+        <v>107</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.503</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:55.781</t>
+          <t>2026-05-29 09:41:18.417</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421977813</v>
+        <v>1780022476280</v>
       </c>
       <c r="C25" t="n">
-        <v>86774</v>
+        <v>85431</v>
       </c>
       <c r="D25" t="n">
-        <v>-514.3099999999999</v>
+        <v>-269.9</v>
       </c>
       <c r="E25" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" t="n">
-        <v>746</v>
+        <v>4197</v>
       </c>
       <c r="G25" t="n">
-        <v>63.09</v>
+        <v>315.76</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2136</v>
+      </c>
+      <c r="L25" t="n">
+        <v>111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.978</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:55.782</t>
+          <t>2026-05-29 09:41:18.419</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421978015</v>
+        <v>1780022476480</v>
       </c>
       <c r="C26" t="n">
-        <v>87049</v>
+        <v>85483</v>
       </c>
       <c r="D26" t="n">
-        <v>-213.6</v>
+        <v>-204.41</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F26" t="n">
-        <v>746</v>
+        <v>4197</v>
       </c>
       <c r="G26" t="n">
-        <v>63.09</v>
+        <v>315.76</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J26" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1938</v>
+      </c>
+      <c r="L26" t="n">
+        <v>119</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.602</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:56.190</t>
+          <t>2026-05-29 09:41:18.451</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421978216</v>
+        <v>1780022476680</v>
       </c>
       <c r="C27" t="n">
-        <v>87286</v>
+        <v>85591</v>
       </c>
       <c r="D27" t="n">
-        <v>34.08</v>
+        <v>-86.19</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F27" t="n">
-        <v>746</v>
+        <v>4197</v>
       </c>
       <c r="G27" t="n">
-        <v>63.09</v>
+        <v>315.76</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L27" t="n">
+        <v>118</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:56.191</t>
+          <t>2026-05-29 09:41:18.467</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421978418</v>
+        <v>1780022476880</v>
       </c>
       <c r="C28" t="n">
-        <v>87452</v>
+        <v>85612</v>
       </c>
       <c r="D28" t="n">
-        <v>198.38</v>
+        <v>-60.88</v>
       </c>
       <c r="E28" t="n">
         <v>82</v>
       </c>
       <c r="F28" t="n">
-        <v>785</v>
+        <v>4197</v>
       </c>
       <c r="G28" t="n">
-        <v>64.22</v>
+        <v>315.76</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1585</v>
+      </c>
+      <c r="L28" t="n">
+        <v>111</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:56.671</t>
+          <t>2026-05-29 09:41:18.469</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421978619</v>
+        <v>1780022477080</v>
       </c>
       <c r="C29" t="n">
-        <v>86740</v>
+        <v>85466</v>
       </c>
       <c r="D29" t="n">
-        <v>-523.54</v>
+        <v>-203.83</v>
       </c>
       <c r="E29" t="n">
         <v>82</v>
       </c>
       <c r="F29" t="n">
-        <v>785</v>
+        <v>4197</v>
       </c>
       <c r="G29" t="n">
-        <v>64.22</v>
+        <v>315.76</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1388</v>
+      </c>
+      <c r="L29" t="n">
+        <v>105</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:56.675</t>
+          <t>2026-05-29 09:41:18.472</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421978820</v>
+        <v>1780022477280</v>
       </c>
       <c r="C30" t="n">
-        <v>86995</v>
+        <v>85775</v>
       </c>
       <c r="D30" t="n">
-        <v>-242.36</v>
+        <v>115.36</v>
       </c>
       <c r="E30" t="n">
         <v>82</v>
       </c>
       <c r="F30" t="n">
-        <v>785</v>
+        <v>4197</v>
       </c>
       <c r="G30" t="n">
-        <v>64.22</v>
+        <v>315.76</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L30" t="n">
+        <v>107</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.203</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:56.917</t>
+          <t>2026-05-29 09:41:18.886</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421979022</v>
+        <v>1780022477480</v>
       </c>
       <c r="C31" t="n">
-        <v>87305</v>
+        <v>85695</v>
       </c>
       <c r="D31" t="n">
-        <v>79.75</v>
+        <v>29.59</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F31" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G31" t="n">
-        <v>66.94</v>
+        <v>315.76</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L31" t="n">
+        <v>107</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.022</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:57.310</t>
+          <t>2026-05-29 09:41:18.887</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421979223</v>
+        <v>1780022477680</v>
       </c>
       <c r="C32" t="n">
-        <v>86609</v>
+        <v>85841</v>
       </c>
       <c r="D32" t="n">
-        <v>-620.23</v>
+        <v>174.11</v>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F32" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G32" t="n">
-        <v>66.94</v>
+        <v>315.76</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J32" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L32" t="n">
+        <v>116</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:57.310</t>
+          <t>2026-05-29 09:41:18.888</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421979425</v>
+        <v>1780022477899</v>
       </c>
       <c r="C33" t="n">
-        <v>86894</v>
+        <v>85595</v>
       </c>
       <c r="D33" t="n">
-        <v>-304.22</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F33" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G33" t="n">
-        <v>66.94</v>
+        <v>315.76</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K33" t="n">
+        <v>988</v>
+      </c>
+      <c r="L33" t="n">
+        <v>114</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:57.635</t>
+          <t>2026-05-29 09:41:19.185</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421979626</v>
+        <v>1780022478099</v>
       </c>
       <c r="C34" t="n">
-        <v>87201</v>
+        <v>85181</v>
       </c>
       <c r="D34" t="n">
-        <v>17.99</v>
+        <v>-490.57</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F34" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G34" t="n">
-        <v>66.94</v>
+        <v>315.76</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L34" t="n">
+        <v>118</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.189</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:57.635</t>
+          <t>2026-05-29 09:41:19.187</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421979828</v>
+        <v>1780022478299</v>
       </c>
       <c r="C35" t="n">
-        <v>87540</v>
+        <v>84983</v>
       </c>
       <c r="D35" t="n">
-        <v>356.09</v>
+        <v>-664.04</v>
       </c>
       <c r="E35" t="n">
         <v>82</v>
       </c>
       <c r="F35" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G35" t="n">
-        <v>65.25</v>
+        <v>315.76</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>887</v>
+      </c>
+      <c r="L35" t="n">
+        <v>109</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.128</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:58.307</t>
+          <t>2026-05-29 09:41:19.807</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421980029</v>
+        <v>1780022478499</v>
       </c>
       <c r="C36" t="n">
-        <v>86631</v>
+        <v>84275</v>
       </c>
       <c r="D36" t="n">
-        <v>-570.71</v>
+        <v>-1338.84</v>
       </c>
       <c r="E36" t="n">
         <v>82</v>
       </c>
       <c r="F36" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G36" t="n">
-        <v>65.25</v>
+        <v>315.76</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L36" t="n">
+        <v>112</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.016</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:58.308</t>
+          <t>2026-05-29 09:41:19.808</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421980230</v>
+        <v>1780022478699</v>
       </c>
       <c r="C37" t="n">
-        <v>87017</v>
+        <v>84263</v>
       </c>
       <c r="D37" t="n">
-        <v>-156.18</v>
+        <v>-1283.89</v>
       </c>
       <c r="E37" t="n">
         <v>82</v>
       </c>
       <c r="F37" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G37" t="n">
-        <v>65.25</v>
+        <v>315.76</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L37" t="n">
+        <v>111</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:58.308</t>
+          <t>2026-05-29 09:41:21.020</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421980432</v>
+        <v>1780022478899</v>
       </c>
       <c r="C38" t="n">
-        <v>87351</v>
+        <v>84342</v>
       </c>
       <c r="D38" t="n">
-        <v>185.63</v>
+        <v>-1140.7</v>
       </c>
       <c r="E38" t="n">
         <v>82</v>
       </c>
       <c r="F38" t="n">
-        <v>685</v>
+        <v>4197</v>
       </c>
       <c r="G38" t="n">
-        <v>65.25</v>
+        <v>315.76</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2120</v>
+      </c>
+      <c r="L38" t="n">
+        <v>108</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:58.651</t>
+          <t>2026-05-29 09:41:21.021</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421980633</v>
+        <v>1780022479099</v>
       </c>
       <c r="C39" t="n">
-        <v>87589</v>
+        <v>84642</v>
       </c>
       <c r="D39" t="n">
-        <v>414.35</v>
+        <v>-783.66</v>
       </c>
       <c r="E39" t="n">
         <v>82</v>
       </c>
       <c r="F39" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G39" t="n">
-        <v>63.17</v>
+        <v>315.76</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1921</v>
+      </c>
+      <c r="L39" t="n">
+        <v>106</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.856</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:58.651</t>
+          <t>2026-05-29 09:41:21.022</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421980835</v>
+        <v>1780022479299</v>
       </c>
       <c r="C40" t="n">
-        <v>86818</v>
+        <v>84943</v>
       </c>
       <c r="D40" t="n">
-        <v>-377.37</v>
+        <v>-443.48</v>
       </c>
       <c r="E40" t="n">
         <v>82</v>
       </c>
       <c r="F40" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G40" t="n">
-        <v>63.17</v>
+        <v>315.76</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1722</v>
+      </c>
+      <c r="L40" t="n">
+        <v>106</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.085</t>
+          <t>2026-05-29 09:41:21.023</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421981036</v>
+        <v>1780022479518</v>
       </c>
       <c r="C41" t="n">
-        <v>87140</v>
+        <v>84937</v>
       </c>
       <c r="D41" t="n">
-        <v>-36.5</v>
+        <v>-427.31</v>
       </c>
       <c r="E41" t="n">
         <v>82</v>
       </c>
       <c r="F41" t="n">
-        <v>745</v>
+        <v>4197</v>
       </c>
       <c r="G41" t="n">
-        <v>63.17</v>
+        <v>315.76</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1504</v>
+      </c>
+      <c r="L41" t="n">
+        <v>111</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.885</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.100</t>
+          <t>2026-05-29 09:41:21.973</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421981237</v>
+        <v>1780022479718</v>
       </c>
       <c r="C42" t="n">
-        <v>87407</v>
+        <v>85197</v>
       </c>
       <c r="D42" t="n">
-        <v>232.32</v>
+        <v>-145.94</v>
       </c>
       <c r="E42" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F42" t="n">
-        <v>765</v>
+        <v>4197</v>
       </c>
       <c r="G42" t="n">
-        <v>51.85</v>
+        <v>315.76</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2253</v>
+      </c>
+      <c r="L42" t="n">
+        <v>109</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.704</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.466</t>
+          <t>2026-05-29 09:41:22.070</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421981439</v>
+        <v>1780022479918</v>
       </c>
       <c r="C43" t="n">
-        <v>86781</v>
+        <v>85314</v>
       </c>
       <c r="D43" t="n">
-        <v>-405.29</v>
+        <v>-21.64</v>
       </c>
       <c r="E43" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F43" t="n">
-        <v>765</v>
+        <v>4197</v>
       </c>
       <c r="G43" t="n">
-        <v>51.85</v>
+        <v>315.76</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2151</v>
+      </c>
+      <c r="L43" t="n">
+        <v>117</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.491</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.467</t>
+          <t>2026-05-29 09:41:22.071</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421981640</v>
+        <v>1780022480118</v>
       </c>
       <c r="C44" t="n">
-        <v>86904</v>
+        <v>85112</v>
       </c>
       <c r="D44" t="n">
-        <v>-262.03</v>
+        <v>-222.56</v>
       </c>
       <c r="E44" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F44" t="n">
-        <v>765</v>
+        <v>4197</v>
       </c>
       <c r="G44" t="n">
-        <v>51.85</v>
+        <v>315.76</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J44" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1952</v>
+      </c>
+      <c r="L44" t="n">
+        <v>108</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.551</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.890</t>
+          <t>2026-05-29 09:41:22.077</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421981842</v>
+        <v>1780022480318</v>
       </c>
       <c r="C45" t="n">
-        <v>87111</v>
+        <v>85153</v>
       </c>
       <c r="D45" t="n">
-        <v>-41.93</v>
+        <v>-170.43</v>
       </c>
       <c r="E45" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F45" t="n">
-        <v>765</v>
+        <v>4197</v>
       </c>
       <c r="G45" t="n">
-        <v>51.85</v>
+        <v>315.76</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J45" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1758</v>
+      </c>
+      <c r="L45" t="n">
+        <v>116</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:59.890</t>
+          <t>2026-05-29 09:41:22.296</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421982043</v>
+        <v>1780022480678</v>
       </c>
       <c r="C46" t="n">
-        <v>87398</v>
+        <v>85078</v>
       </c>
       <c r="D46" t="n">
-        <v>247.17</v>
+        <v>-236.91</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F46" t="n">
-        <v>766</v>
+        <v>4197</v>
       </c>
       <c r="G46" t="n">
-        <v>50.5</v>
+        <v>315.76</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1617</v>
+      </c>
+      <c r="L46" t="n">
+        <v>113</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:00.420</t>
+          <t>2026-05-29 09:41:22.296</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421982244</v>
+        <v>1780022480878</v>
       </c>
       <c r="C47" t="n">
-        <v>86664</v>
+        <v>85090</v>
       </c>
       <c r="D47" t="n">
-        <v>-499.19</v>
+        <v>-213.07</v>
       </c>
       <c r="E47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F47" t="n">
-        <v>766</v>
+        <v>4197</v>
       </c>
       <c r="G47" t="n">
-        <v>50.5</v>
+        <v>315.76</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L47" t="n">
+        <v>121</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.553</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:00.421</t>
+          <t>2026-05-29 09:41:22.297</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421982446</v>
+        <v>1780022481097</v>
       </c>
       <c r="C48" t="n">
-        <v>87032</v>
+        <v>85410</v>
       </c>
       <c r="D48" t="n">
-        <v>-106.23</v>
+        <v>117.59</v>
       </c>
       <c r="E48" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F48" t="n">
-        <v>766</v>
+        <v>6276</v>
       </c>
       <c r="G48" t="n">
-        <v>50.5</v>
+        <v>315.76</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:00.697</t>
+          <t>2026-05-29 09:41:22.758</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421982647</v>
+        <v>1780022481297</v>
       </c>
       <c r="C49" t="n">
-        <v>87401</v>
+        <v>85499</v>
       </c>
       <c r="D49" t="n">
-        <v>268.08</v>
+        <v>200.71</v>
       </c>
       <c r="E49" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F49" t="n">
-        <v>624</v>
+        <v>6276</v>
       </c>
       <c r="G49" t="n">
-        <v>55.5</v>
+        <v>315.76</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1460</v>
+      </c>
+      <c r="L49" t="n">
+        <v>107</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.749</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:00.697</t>
+          <t>2026-05-29 09:41:22.777</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421982849</v>
+        <v>1780022481497</v>
       </c>
       <c r="C50" t="n">
-        <v>86636</v>
+        <v>85933</v>
       </c>
       <c r="D50" t="n">
-        <v>-510.32</v>
+        <v>624.67</v>
       </c>
       <c r="E50" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F50" t="n">
-        <v>624</v>
+        <v>6276</v>
       </c>
       <c r="G50" t="n">
-        <v>55.5</v>
+        <v>315.76</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1279</v>
+      </c>
+      <c r="L50" t="n">
+        <v>115</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.742</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.221</t>
+          <t>2026-05-29 09:41:23.831</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421983050</v>
+        <v>1780022481698</v>
       </c>
       <c r="C51" t="n">
-        <v>86860</v>
+        <v>86535</v>
       </c>
       <c r="D51" t="n">
-        <v>-260.81</v>
+        <v>1195.44</v>
       </c>
       <c r="E51" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F51" t="n">
-        <v>624</v>
+        <v>6276</v>
       </c>
       <c r="G51" t="n">
-        <v>55.5</v>
+        <v>315.76</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2132</v>
+      </c>
+      <c r="L51" t="n">
+        <v>106</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.224</t>
+          <t>2026-05-29 09:41:23.861</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421983252</v>
+        <v>1780022481897</v>
       </c>
       <c r="C52" t="n">
-        <v>87118</v>
+        <v>85934</v>
       </c>
       <c r="D52" t="n">
-        <v>10.24</v>
+        <v>534.67</v>
       </c>
       <c r="E52" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F52" t="n">
-        <v>624</v>
+        <v>6276</v>
       </c>
       <c r="G52" t="n">
-        <v>55.5</v>
+        <v>315.76</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1963</v>
+      </c>
+      <c r="L52" t="n">
+        <v>122</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.597</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.534</t>
+          <t>2026-05-29 09:41:23.863</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421983453</v>
+        <v>1780022482097</v>
       </c>
       <c r="C53" t="n">
-        <v>87442</v>
+        <v>85225</v>
       </c>
       <c r="D53" t="n">
-        <v>333.72</v>
+        <v>-201.07</v>
       </c>
       <c r="E53" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F53" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G53" t="n">
-        <v>49.17</v>
+        <v>315.76</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1765</v>
+      </c>
+      <c r="L53" t="n">
+        <v>108</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.522</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.534</t>
+          <t>2026-05-29 09:41:23.864</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421983654</v>
+        <v>1780022482297</v>
       </c>
       <c r="C54" t="n">
-        <v>86542</v>
+        <v>84937</v>
       </c>
       <c r="D54" t="n">
-        <v>-582.96</v>
+        <v>-479.01</v>
       </c>
       <c r="E54" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F54" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G54" t="n">
-        <v>49.17</v>
+        <v>315.76</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1566</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.499</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.956</t>
+          <t>2026-05-29 09:41:26.443</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421983856</v>
+        <v>1780022482497</v>
       </c>
       <c r="C55" t="n">
-        <v>86802</v>
+        <v>85444</v>
       </c>
       <c r="D55" t="n">
-        <v>-293.81</v>
+        <v>51.94</v>
       </c>
       <c r="E55" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F55" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G55" t="n">
-        <v>49.17</v>
+        <v>315.76</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3945</v>
+      </c>
+      <c r="L55" t="n">
+        <v>107</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.058</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:01.971</t>
+          <t>2026-05-29 09:41:26.455</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421984057</v>
+        <v>1780022482716</v>
       </c>
       <c r="C56" t="n">
-        <v>87036</v>
+        <v>84772</v>
       </c>
       <c r="D56" t="n">
-        <v>-45.12</v>
+        <v>-622.66</v>
       </c>
       <c r="E56" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G56" t="n">
-        <v>49.17</v>
+        <v>315.76</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J56" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3738</v>
+      </c>
+      <c r="L56" t="n">
+        <v>122</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.427</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:02.420</t>
+          <t>2026-05-29 09:41:26.459</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421984259</v>
+        <v>1780022482917</v>
       </c>
       <c r="C57" t="n">
-        <v>87098</v>
+        <v>84321</v>
       </c>
       <c r="D57" t="n">
-        <v>19.13</v>
+        <v>-1042.53</v>
       </c>
       <c r="E57" t="n">
         <v>82</v>
       </c>
       <c r="F57" t="n">
-        <v>806</v>
+        <v>6276</v>
       </c>
       <c r="G57" t="n">
-        <v>54.82</v>
+        <v>315.76</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J57" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3540</v>
+      </c>
+      <c r="L57" t="n">
+        <v>107</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:02.420</t>
+          <t>2026-05-29 09:41:26.723</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421984460</v>
+        <v>1780022483116</v>
       </c>
       <c r="C58" t="n">
-        <v>86504</v>
+        <v>84007</v>
       </c>
       <c r="D58" t="n">
-        <v>-575.8200000000001</v>
+        <v>-1304.4</v>
       </c>
       <c r="E58" t="n">
         <v>82</v>
       </c>
       <c r="F58" t="n">
-        <v>806</v>
+        <v>6276</v>
       </c>
       <c r="G58" t="n">
-        <v>54.82</v>
+        <v>315.76</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J58" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3605</v>
+      </c>
+      <c r="L58" t="n">
+        <v>112</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:02.760</t>
+          <t>2026-05-29 09:41:26.756</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421984661</v>
+        <v>1780022485596</v>
       </c>
       <c r="C59" t="n">
-        <v>86777</v>
+        <v>84094</v>
       </c>
       <c r="D59" t="n">
-        <v>-274.03</v>
+        <v>-1152.18</v>
       </c>
       <c r="E59" t="n">
         <v>82</v>
       </c>
       <c r="F59" t="n">
-        <v>806</v>
+        <v>6276</v>
       </c>
       <c r="G59" t="n">
-        <v>54.82</v>
+        <v>315.76</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L59" t="n">
+        <v>107</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:02.761</t>
+          <t>2026-05-29 09:41:26.758</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421984863</v>
+        <v>1780022485814</v>
       </c>
       <c r="C60" t="n">
-        <v>87112</v>
+        <v>84546</v>
       </c>
       <c r="D60" t="n">
-        <v>74.67</v>
+        <v>-642.5700000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F60" t="n">
-        <v>685</v>
+        <v>6276</v>
       </c>
       <c r="G60" t="n">
-        <v>56.84</v>
+        <v>315.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>943</v>
+      </c>
+      <c r="L60" t="n">
+        <v>116</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.239</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.200</t>
+          <t>2026-05-29 09:41:28.162</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421985064</v>
+        <v>1780022486014</v>
       </c>
       <c r="C61" t="n">
-        <v>86385</v>
+        <v>85373</v>
       </c>
       <c r="D61" t="n">
-        <v>-656.0599999999999</v>
+        <v>216.56</v>
       </c>
       <c r="E61" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F61" t="n">
-        <v>685</v>
+        <v>6276</v>
       </c>
       <c r="G61" t="n">
-        <v>56.84</v>
+        <v>315.76</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2147</v>
+      </c>
+      <c r="L61" t="n">
+        <v>116</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.198</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.201</t>
+          <t>2026-05-29 09:41:28.163</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421985266</v>
+        <v>1780022486214</v>
       </c>
       <c r="C62" t="n">
-        <v>86702</v>
+        <v>85569</v>
       </c>
       <c r="D62" t="n">
-        <v>-306.26</v>
+        <v>401.73</v>
       </c>
       <c r="E62" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F62" t="n">
-        <v>685</v>
+        <v>6276</v>
       </c>
       <c r="G62" t="n">
-        <v>56.84</v>
+        <v>315.76</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1949</v>
+      </c>
+      <c r="L62" t="n">
+        <v>119</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.838</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.603</t>
+          <t>2026-05-29 09:41:28.164</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421985467</v>
+        <v>1780022486415</v>
       </c>
       <c r="C63" t="n">
-        <v>86829</v>
+        <v>85327</v>
       </c>
       <c r="D63" t="n">
-        <v>-163.95</v>
+        <v>139.64</v>
       </c>
       <c r="E63" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F63" t="n">
-        <v>685</v>
+        <v>6276</v>
       </c>
       <c r="G63" t="n">
-        <v>56.84</v>
+        <v>315.76</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1749</v>
+      </c>
+      <c r="L63" t="n">
+        <v>108</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.842</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.604</t>
+          <t>2026-05-29 09:41:28.166</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421985669</v>
+        <v>1780022486614</v>
       </c>
       <c r="C64" t="n">
-        <v>87175</v>
+        <v>84494</v>
       </c>
       <c r="D64" t="n">
-        <v>190.25</v>
+        <v>-700.34</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F64" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G64" t="n">
-        <v>53.79</v>
+        <v>315.76</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1551</v>
+      </c>
+      <c r="L64" t="n">
+        <v>125</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.579</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.991</t>
+          <t>2026-05-29 09:41:28.168</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421985870</v>
+        <v>1780022486814</v>
       </c>
       <c r="C65" t="n">
-        <v>86339</v>
+        <v>86261</v>
       </c>
       <c r="D65" t="n">
-        <v>-655.26</v>
+        <v>1101.68</v>
       </c>
       <c r="E65" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G65" t="n">
-        <v>53.79</v>
+        <v>315.76</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1353</v>
+      </c>
+      <c r="L65" t="n">
+        <v>107</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:03.992</t>
+          <t>2026-05-29 09:41:28.169</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421986071</v>
+        <v>1780022487033</v>
       </c>
       <c r="C66" t="n">
-        <v>86649</v>
+        <v>85619</v>
       </c>
       <c r="D66" t="n">
-        <v>-312.5</v>
+        <v>404.59</v>
       </c>
       <c r="E66" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F66" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G66" t="n">
-        <v>53.79</v>
+        <v>315.76</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1136</v>
+      </c>
+      <c r="L66" t="n">
+        <v>111</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:04.387</t>
+          <t>2026-05-29 09:41:28.358</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421986273</v>
+        <v>1780022487233</v>
       </c>
       <c r="C67" t="n">
-        <v>86950</v>
+        <v>85354</v>
       </c>
       <c r="D67" t="n">
-        <v>4.12</v>
+        <v>119.36</v>
       </c>
       <c r="E67" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F67" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G67" t="n">
-        <v>53.79</v>
+        <v>315.76</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L67" t="n">
+        <v>110</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.276</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:04.387</t>
+          <t>2026-05-29 09:41:28.412</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421986474</v>
+        <v>1780022487433</v>
       </c>
       <c r="C68" t="n">
-        <v>87256</v>
+        <v>85083</v>
       </c>
       <c r="D68" t="n">
-        <v>309.92</v>
+        <v>-157.6</v>
       </c>
       <c r="E68" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F68" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G68" t="n">
-        <v>52.14</v>
+        <v>315.76</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J68" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K68" t="n">
+        <v>978</v>
+      </c>
+      <c r="L68" t="n">
+        <v>122</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.025</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:04.816</t>
+          <t>2026-05-29 09:41:28.817</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421986676</v>
+        <v>1780022487634</v>
       </c>
       <c r="C69" t="n">
-        <v>86313</v>
+        <v>84329</v>
       </c>
       <c r="D69" t="n">
-        <v>-648.58</v>
+        <v>-903.72</v>
       </c>
       <c r="E69" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F69" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G69" t="n">
-        <v>52.14</v>
+        <v>315.76</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L69" t="n">
+        <v>106</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.335</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:04.816</t>
+          <t>2026-05-29 09:41:28.819</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421986877</v>
+        <v>1780022487833</v>
       </c>
       <c r="C70" t="n">
-        <v>86626</v>
+        <v>84827</v>
       </c>
       <c r="D70" t="n">
-        <v>-303.15</v>
+        <v>-360.54</v>
       </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F70" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G70" t="n">
-        <v>52.14</v>
+        <v>315.76</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>985</v>
+      </c>
+      <c r="L70" t="n">
+        <v>116</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.917</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:04.817</t>
+          <t>2026-05-29 09:41:30.869</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421987078</v>
+        <v>1780022488034</v>
       </c>
       <c r="C71" t="n">
-        <v>86879</v>
+        <v>85422</v>
       </c>
       <c r="D71" t="n">
-        <v>-34.99</v>
+        <v>252.49</v>
       </c>
       <c r="E71" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F71" t="n">
-        <v>745</v>
+        <v>6276</v>
       </c>
       <c r="G71" t="n">
-        <v>52.14</v>
+        <v>315.76</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2834</v>
+      </c>
+      <c r="L71" t="n">
+        <v>108</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.492</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:05.223</t>
+          <t>2026-05-29 09:41:30.870</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421987280</v>
+        <v>1780022488234</v>
       </c>
       <c r="C72" t="n">
-        <v>86654</v>
+        <v>84879</v>
       </c>
       <c r="D72" t="n">
-        <v>-258.24</v>
+        <v>-303.14</v>
       </c>
       <c r="E72" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F72" t="n">
-        <v>786</v>
+        <v>6276</v>
       </c>
       <c r="G72" t="n">
-        <v>52</v>
+        <v>315.76</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2635</v>
+      </c>
+      <c r="L72" t="n">
+        <v>109</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.509</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:05.224</t>
+          <t>2026-05-29 09:41:30.871</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421987481</v>
+        <v>1780022488434</v>
       </c>
       <c r="C73" t="n">
-        <v>86392</v>
+        <v>84139</v>
       </c>
       <c r="D73" t="n">
-        <v>-507.33</v>
+        <v>-1027.98</v>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F73" t="n">
-        <v>786</v>
+        <v>6276</v>
       </c>
       <c r="G73" t="n">
-        <v>52</v>
+        <v>315.76</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2436</v>
+      </c>
+      <c r="L73" t="n">
+        <v>99</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.502</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:05.728</t>
+          <t>2026-05-29 09:41:30.871</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421987683</v>
+        <v>1780022488652</v>
       </c>
       <c r="C74" t="n">
-        <v>86649</v>
+        <v>83857</v>
       </c>
       <c r="D74" t="n">
-        <v>-224.96</v>
+        <v>-1258.58</v>
       </c>
       <c r="E74" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F74" t="n">
-        <v>786</v>
+        <v>6276</v>
       </c>
       <c r="G74" t="n">
-        <v>52</v>
+        <v>315.76</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2219</v>
+      </c>
+      <c r="L74" t="n">
+        <v>123</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.521</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:05.730</t>
+          <t>2026-05-29 09:41:31.147</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421987884</v>
+        <v>1780022488852</v>
       </c>
       <c r="C75" t="n">
-        <v>86978</v>
+        <v>84099</v>
       </c>
       <c r="D75" t="n">
-        <v>115.29</v>
+        <v>-953.65</v>
       </c>
       <c r="E75" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F75" t="n">
-        <v>725</v>
+        <v>6276</v>
       </c>
       <c r="G75" t="n">
-        <v>52.23</v>
+        <v>315.76</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2294</v>
+      </c>
+      <c r="L75" t="n">
+        <v>105</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.122</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.042</t>
+          <t>2026-05-29 09:41:31.148</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421988086</v>
+        <v>1780022489052</v>
       </c>
       <c r="C76" t="n">
-        <v>86177</v>
+        <v>83917</v>
       </c>
       <c r="D76" t="n">
-        <v>-691.48</v>
+        <v>-1087.97</v>
       </c>
       <c r="E76" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F76" t="n">
-        <v>725</v>
+        <v>6276</v>
       </c>
       <c r="G76" t="n">
-        <v>52.23</v>
+        <v>315.76</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2095</v>
+      </c>
+      <c r="L76" t="n">
+        <v>122</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.742</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.042</t>
+          <t>2026-05-29 09:41:31.149</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421988287</v>
+        <v>1780022489253</v>
       </c>
       <c r="C77" t="n">
-        <v>86528</v>
+        <v>83466</v>
       </c>
       <c r="D77" t="n">
-        <v>-305.91</v>
+        <v>-1484.57</v>
       </c>
       <c r="E77" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F77" t="n">
-        <v>725</v>
+        <v>6276</v>
       </c>
       <c r="G77" t="n">
-        <v>52.23</v>
+        <v>315.76</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1895</v>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.839</t>
+          <t>2026-05-29 09:41:31.879</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421988488</v>
+        <v>1780022489452</v>
       </c>
       <c r="C78" t="n">
-        <v>86898</v>
+        <v>83377</v>
       </c>
       <c r="D78" t="n">
-        <v>79.39</v>
+        <v>-1499.34</v>
       </c>
       <c r="E78" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F78" t="n">
-        <v>725</v>
+        <v>6276</v>
       </c>
       <c r="G78" t="n">
-        <v>52.23</v>
+        <v>315.76</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2425</v>
+      </c>
+      <c r="L78" t="n">
+        <v>95</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.840</t>
+          <t>2026-05-29 09:41:31.888</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421988690</v>
+        <v>1780022489652</v>
       </c>
       <c r="C79" t="n">
-        <v>87190</v>
+        <v>82921</v>
       </c>
       <c r="D79" t="n">
-        <v>367.42</v>
+        <v>-1880.37</v>
       </c>
       <c r="E79" t="n">
         <v>82</v>
       </c>
       <c r="F79" t="n">
-        <v>665</v>
+        <v>6276</v>
       </c>
       <c r="G79" t="n">
-        <v>56.16</v>
+        <v>315.76</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2235</v>
+      </c>
+      <c r="L79" t="n">
+        <v>118</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.022</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.840</t>
+          <t>2026-05-29 09:41:32.114</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421988891</v>
+        <v>1780022489852</v>
       </c>
       <c r="C80" t="n">
-        <v>86323</v>
+        <v>83212</v>
       </c>
       <c r="D80" t="n">
-        <v>-517.95</v>
+        <v>-1495.36</v>
       </c>
       <c r="E80" t="n">
         <v>82</v>
       </c>
       <c r="F80" t="n">
-        <v>665</v>
+        <v>6276</v>
       </c>
       <c r="G80" t="n">
-        <v>56.16</v>
+        <v>315.76</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J80" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2261</v>
+      </c>
+      <c r="L80" t="n">
+        <v>113</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:06.841</t>
+          <t>2026-05-29 09:41:32.116</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421989093</v>
+        <v>1780022490512</v>
       </c>
       <c r="C81" t="n">
-        <v>86702</v>
+        <v>84410</v>
       </c>
       <c r="D81" t="n">
-        <v>-113.05</v>
+        <v>-222.59</v>
       </c>
       <c r="E81" t="n">
         <v>82</v>
       </c>
       <c r="F81" t="n">
-        <v>665</v>
+        <v>6276</v>
       </c>
       <c r="G81" t="n">
-        <v>56.16</v>
+        <v>315.76</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J81" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L81" t="n">
+        <v>107</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.961</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:07.266</t>
+          <t>2026-05-29 09:41:32.117</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421989294</v>
+        <v>1780022490711</v>
       </c>
       <c r="C82" t="n">
-        <v>86992</v>
+        <v>84375</v>
       </c>
       <c r="D82" t="n">
-        <v>182.6</v>
+        <v>-246.46</v>
       </c>
       <c r="E82" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F82" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G82" t="n">
-        <v>56.09</v>
+        <v>315.76</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L82" t="n">
+        <v>121</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:07.269</t>
+          <t>2026-05-29 09:41:32.118</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421989496</v>
+        <v>1780022490911</v>
       </c>
       <c r="C83" t="n">
-        <v>86978</v>
+        <v>84972</v>
       </c>
       <c r="D83" t="n">
-        <v>159.47</v>
+        <v>362.86</v>
       </c>
       <c r="E83" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F83" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G83" t="n">
-        <v>56.09</v>
+        <v>315.76</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L83" t="n">
+        <v>104</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.971</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:07.806</t>
+          <t>2026-05-29 09:41:32.246</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421989697</v>
+        <v>1780022491111</v>
       </c>
       <c r="C84" t="n">
-        <v>86239</v>
+        <v>85672</v>
       </c>
       <c r="D84" t="n">
-        <v>-587.5</v>
+        <v>1044.72</v>
       </c>
       <c r="E84" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F84" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G84" t="n">
-        <v>56.09</v>
+        <v>315.76</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1134</v>
+      </c>
+      <c r="L84" t="n">
+        <v>106</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.803</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:07.807</t>
+          <t>2026-05-29 09:41:32.255</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421989898</v>
+        <v>1780022491311</v>
       </c>
       <c r="C85" t="n">
-        <v>86606</v>
+        <v>85276</v>
       </c>
       <c r="D85" t="n">
-        <v>-191.13</v>
+        <v>596.49</v>
       </c>
       <c r="E85" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F85" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G85" t="n">
-        <v>56.09</v>
+        <v>315.76</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>943</v>
+      </c>
+      <c r="L85" t="n">
+        <v>121</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.781</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:08.290</t>
+          <t>2026-05-29 09:41:32.587</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421990100</v>
+        <v>1780022491531</v>
       </c>
       <c r="C86" t="n">
-        <v>86905</v>
+        <v>84848</v>
       </c>
       <c r="D86" t="n">
-        <v>117.43</v>
+        <v>138.66</v>
       </c>
       <c r="E86" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F86" t="n">
-        <v>826</v>
+        <v>9614</v>
       </c>
       <c r="G86" t="n">
-        <v>50.09</v>
+        <v>315.76</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1054</v>
+      </c>
+      <c r="L86" t="n">
+        <v>106</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.255</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:08.290</t>
+          <t>2026-05-29 09:41:32.600</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421990301</v>
+        <v>1780022491730</v>
       </c>
       <c r="C87" t="n">
-        <v>86705</v>
+        <v>83499</v>
       </c>
       <c r="D87" t="n">
-        <v>-88.44</v>
+        <v>-1217.27</v>
       </c>
       <c r="E87" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F87" t="n">
-        <v>826</v>
+        <v>9614</v>
       </c>
       <c r="G87" t="n">
-        <v>50.09</v>
+        <v>315.76</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K87" t="n">
+        <v>869</v>
+      </c>
+      <c r="L87" t="n">
+        <v>119</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.952</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:08.291</t>
+          <t>2026-05-29 09:41:32.889</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421990503</v>
+        <v>1780022491930</v>
       </c>
       <c r="C88" t="n">
-        <v>86405</v>
+        <v>82551</v>
       </c>
       <c r="D88" t="n">
-        <v>-384.02</v>
+        <v>-2104.41</v>
       </c>
       <c r="E88" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F88" t="n">
-        <v>826</v>
+        <v>9614</v>
       </c>
       <c r="G88" t="n">
-        <v>50.09</v>
+        <v>315.76</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K88" t="n">
+        <v>958</v>
+      </c>
+      <c r="L88" t="n">
+        <v>117</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.234</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:08.689</t>
+          <t>2026-05-29 09:41:33.244</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421990704</v>
+        <v>1780022492131</v>
       </c>
       <c r="C89" t="n">
-        <v>86635</v>
+        <v>81646</v>
       </c>
       <c r="D89" t="n">
-        <v>-134.82</v>
+        <v>-2904.19</v>
       </c>
       <c r="E89" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F89" t="n">
-        <v>826</v>
+        <v>9614</v>
       </c>
       <c r="G89" t="n">
-        <v>50.09</v>
+        <v>315.76</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1112</v>
+      </c>
+      <c r="L89" t="n">
+        <v>107</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:08.690</t>
+          <t>2026-05-29 09:41:33.245</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421990906</v>
+        <v>1780022492330</v>
       </c>
       <c r="C90" t="n">
-        <v>86952</v>
+        <v>82291</v>
       </c>
       <c r="D90" t="n">
-        <v>188.92</v>
+        <v>-2113.98</v>
       </c>
       <c r="E90" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F90" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G90" t="n">
-        <v>50.29</v>
+        <v>315.76</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>914</v>
+      </c>
+      <c r="L90" t="n">
+        <v>128</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.163</t>
+          <t>2026-05-29 09:41:33.247</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421991107</v>
+        <v>1780022492530</v>
       </c>
       <c r="C91" t="n">
-        <v>86235</v>
+        <v>82736</v>
       </c>
       <c r="D91" t="n">
-        <v>-537.53</v>
+        <v>-1563.28</v>
       </c>
       <c r="E91" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F91" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G91" t="n">
-        <v>50.29</v>
+        <v>315.76</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K91" t="n">
+        <v>716</v>
+      </c>
+      <c r="L91" t="n">
+        <v>109</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.164</t>
+          <t>2026-05-29 09:41:33.851</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421991308</v>
+        <v>1780022492730</v>
       </c>
       <c r="C92" t="n">
-        <v>86610</v>
+        <v>82717</v>
       </c>
       <c r="D92" t="n">
-        <v>-135.65</v>
+        <v>-1504.12</v>
       </c>
       <c r="E92" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F92" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G92" t="n">
-        <v>50.29</v>
+        <v>315.76</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L92" t="n">
+        <v>113</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.587</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.520</t>
+          <t>2026-05-29 09:41:33.853</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421991510</v>
+        <v>1780022492930</v>
       </c>
       <c r="C93" t="n">
-        <v>86914</v>
+        <v>83850</v>
       </c>
       <c r="D93" t="n">
-        <v>175.13</v>
+        <v>-295.91</v>
       </c>
       <c r="E93" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F93" t="n">
-        <v>765</v>
+        <v>9614</v>
       </c>
       <c r="G93" t="n">
-        <v>50.29</v>
+        <v>315.76</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>922</v>
+      </c>
+      <c r="L93" t="n">
+        <v>108</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.239</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.520</t>
+          <t>2026-05-29 09:41:34.659</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421991711</v>
+        <v>1780022493149</v>
       </c>
       <c r="C94" t="n">
-        <v>87217</v>
+        <v>82529</v>
       </c>
       <c r="D94" t="n">
-        <v>469.38</v>
+        <v>-1602.11</v>
       </c>
       <c r="E94" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F94" t="n">
-        <v>685</v>
+        <v>9614</v>
       </c>
       <c r="G94" t="n">
-        <v>50.23</v>
+        <v>315.76</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L94" t="n">
+        <v>109</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.711</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.938</t>
+          <t>2026-05-29 09:41:34.660</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421991913</v>
+        <v>1780022493349</v>
       </c>
       <c r="C95" t="n">
-        <v>86462</v>
+        <v>82198</v>
       </c>
       <c r="D95" t="n">
-        <v>-309.09</v>
+        <v>-1853.01</v>
       </c>
       <c r="E95" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F95" t="n">
-        <v>685</v>
+        <v>9614</v>
       </c>
       <c r="G95" t="n">
-        <v>50.23</v>
+        <v>315.76</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L95" t="n">
+        <v>101</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.819</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:09.939</t>
+          <t>2026-05-29 09:41:34.661</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421992114</v>
+        <v>1780022493549</v>
       </c>
       <c r="C96" t="n">
-        <v>86713</v>
+        <v>82237</v>
       </c>
       <c r="D96" t="n">
-        <v>-42.64</v>
+        <v>-1721.36</v>
       </c>
       <c r="E96" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F96" t="n">
-        <v>685</v>
+        <v>9614</v>
       </c>
       <c r="G96" t="n">
-        <v>50.23</v>
+        <v>315.76</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L96" t="n">
+        <v>103</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:10.350</t>
+          <t>2026-05-29 09:41:34.904</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421992315</v>
+        <v>1780022493749</v>
       </c>
       <c r="C97" t="n">
-        <v>87089</v>
+        <v>81965</v>
       </c>
       <c r="D97" t="n">
-        <v>335.49</v>
+        <v>-1907.29</v>
       </c>
       <c r="E97" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F97" t="n">
-        <v>725</v>
+        <v>9614</v>
       </c>
       <c r="G97" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L97" t="n">
+        <v>126</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.049</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:10.350</t>
+          <t>2026-05-29 09:41:34.906</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421992517</v>
+        <v>1780022493949</v>
       </c>
       <c r="C98" t="n">
-        <v>86466</v>
+        <v>82139</v>
       </c>
       <c r="D98" t="n">
-        <v>-304.28</v>
+        <v>-1637.93</v>
       </c>
       <c r="E98" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F98" t="n">
-        <v>725</v>
+        <v>9614</v>
       </c>
       <c r="G98" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>956</v>
+      </c>
+      <c r="L98" t="n">
+        <v>120</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:10.730</t>
+          <t>2026-05-29 09:41:34.909</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421992718</v>
+        <v>1780022494149</v>
       </c>
       <c r="C99" t="n">
-        <v>86691</v>
+        <v>82434</v>
       </c>
       <c r="D99" t="n">
-        <v>-64.06999999999999</v>
+        <v>-1261.03</v>
       </c>
       <c r="E99" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F99" t="n">
-        <v>725</v>
+        <v>9614</v>
       </c>
       <c r="G99" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>758</v>
+      </c>
+      <c r="L99" t="n">
+        <v>116</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.975</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:10.731</t>
+          <t>2026-05-29 09:41:35.535</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421992920</v>
+        <v>1780022494349</v>
       </c>
       <c r="C100" t="n">
-        <v>86938</v>
+        <v>82725</v>
       </c>
       <c r="D100" t="n">
-        <v>186.14</v>
+        <v>-906.98</v>
       </c>
       <c r="E100" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F100" t="n">
-        <v>725</v>
+        <v>9614</v>
       </c>
       <c r="G100" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L100" t="n">
+        <v>117</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:11.423</t>
+          <t>2026-05-29 09:41:35.543</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421993121</v>
+        <v>1780022494568</v>
       </c>
       <c r="C101" t="n">
-        <v>87271</v>
+        <v>82921</v>
       </c>
       <c r="D101" t="n">
-        <v>509.83</v>
+        <v>-665.63</v>
       </c>
       <c r="E101" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>9614</v>
       </c>
       <c r="G101" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>974</v>
+      </c>
+      <c r="L101" t="n">
+        <v>108</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.523</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:11.424</t>
+          <t>2026-05-29 09:41:36.707</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421993322</v>
+        <v>1780022494768</v>
       </c>
       <c r="C102" t="n">
-        <v>86442</v>
+        <v>81873</v>
       </c>
       <c r="D102" t="n">
-        <v>-344.66</v>
+        <v>-1680.35</v>
       </c>
       <c r="E102" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F102" t="n">
-        <v>745</v>
+        <v>9614</v>
       </c>
       <c r="G102" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1938</v>
+      </c>
+      <c r="L102" t="n">
+        <v>121</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.239</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:11.764</t>
+          <t>2026-05-29 09:41:36.737</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421993524</v>
+        <v>1780022494968</v>
       </c>
       <c r="C103" t="n">
-        <v>86757</v>
+        <v>81902</v>
       </c>
       <c r="D103" t="n">
-        <v>-12.43</v>
+        <v>-1567.33</v>
       </c>
       <c r="E103" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F103" t="n">
-        <v>745</v>
+        <v>9614</v>
       </c>
       <c r="G103" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1767</v>
+      </c>
+      <c r="L103" t="n">
+        <v>108</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.482</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:11.765</t>
+          <t>2026-05-29 09:41:36.738</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421993725</v>
+        <v>1780022495168</v>
       </c>
       <c r="C104" t="n">
-        <v>87081</v>
+        <v>82586</v>
       </c>
       <c r="D104" t="n">
-        <v>312.19</v>
+        <v>-804.96</v>
       </c>
       <c r="E104" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F104" t="n">
-        <v>745</v>
+        <v>9614</v>
       </c>
       <c r="G104" t="n">
-        <v>46.92</v>
+        <v>315.76</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1569</v>
+      </c>
+      <c r="L104" t="n">
+        <v>114</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.059</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:11.766</t>
+          <t>2026-05-29 09:41:36.747</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421993927</v>
+        <v>1780022495368</v>
       </c>
       <c r="C105" t="n">
-        <v>86771</v>
+        <v>81997</v>
       </c>
       <c r="D105" t="n">
-        <v>-13.42</v>
+        <v>-1353.72</v>
       </c>
       <c r="E105" t="n">
         <v>82</v>
       </c>
       <c r="F105" t="n">
-        <v>725</v>
+        <v>4597</v>
       </c>
       <c r="G105" t="n">
-        <v>47.26</v>
+        <v>315.76</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1378</v>
+      </c>
+      <c r="L105" t="n">
+        <v>111</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.213</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:12.174</t>
+          <t>2026-05-29 09:41:36.748</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421994128</v>
+        <v>1780022495568</v>
       </c>
       <c r="C106" t="n">
-        <v>86782</v>
+        <v>82288</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.75</v>
+        <v>-995.03</v>
       </c>
       <c r="E106" t="n">
         <v>82</v>
       </c>
       <c r="F106" t="n">
-        <v>725</v>
+        <v>4597</v>
       </c>
       <c r="G106" t="n">
-        <v>47.26</v>
+        <v>315.76</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1179</v>
+      </c>
+      <c r="L106" t="n">
+        <v>115</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.023</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:12.175</t>
+          <t>2026-05-29 09:41:36.833</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421994329</v>
+        <v>1780022495768</v>
       </c>
       <c r="C107" t="n">
-        <v>87108</v>
+        <v>82560</v>
       </c>
       <c r="D107" t="n">
-        <v>324.34</v>
+        <v>-673.28</v>
       </c>
       <c r="E107" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F107" t="n">
-        <v>725</v>
+        <v>520</v>
       </c>
       <c r="G107" t="n">
-        <v>47.26</v>
+        <v>338.95</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L107" t="n">
+        <v>116</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.113</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:12.577</t>
+          <t>2026-05-29 09:41:36.973</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421994531</v>
+        <v>1780022495968</v>
       </c>
       <c r="C108" t="n">
-        <v>87521</v>
+        <v>82259</v>
       </c>
       <c r="D108" t="n">
-        <v>721.12</v>
+        <v>-940.61</v>
       </c>
       <c r="E108" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F108" t="n">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="G108" t="n">
-        <v>49.93</v>
+        <v>338.95</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L108" t="n">
+        <v>104</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.728</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:12.578</t>
+          <t>2026-05-29 09:41:37.116</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421994732</v>
+        <v>1780022496187</v>
       </c>
       <c r="C109" t="n">
-        <v>86695</v>
+        <v>82945</v>
       </c>
       <c r="D109" t="n">
-        <v>-140.93</v>
+        <v>-207.58</v>
       </c>
       <c r="E109" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F109" t="n">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="G109" t="n">
-        <v>49.93</v>
+        <v>338.95</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K109" t="n">
+        <v>927</v>
+      </c>
+      <c r="L109" t="n">
+        <v>112</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:13.018</t>
+          <t>2026-05-29 09:41:37.118</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421994934</v>
+        <v>1780022496387</v>
       </c>
       <c r="C110" t="n">
-        <v>87037</v>
+        <v>81362</v>
       </c>
       <c r="D110" t="n">
-        <v>208.11</v>
+        <v>-1780.2</v>
       </c>
       <c r="E110" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F110" t="n">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="G110" t="n">
-        <v>49.93</v>
+        <v>338.95</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>729</v>
+      </c>
+      <c r="L110" t="n">
+        <v>105</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.347</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:13.018</t>
+          <t>2026-05-29 09:41:37.746</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421995135</v>
+        <v>1780022496587</v>
       </c>
       <c r="C111" t="n">
-        <v>87387</v>
+        <v>83425</v>
       </c>
       <c r="D111" t="n">
-        <v>547.71</v>
+        <v>371.81</v>
       </c>
       <c r="E111" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>705</v>
+        <v>520</v>
       </c>
       <c r="G111" t="n">
-        <v>50.51</v>
+        <v>338.95</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L111" t="n">
+        <v>113</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.673</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:13.370</t>
+          <t>2026-05-29 09:41:37.748</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421995336</v>
+        <v>1780022496787</v>
       </c>
       <c r="C112" t="n">
-        <v>86927</v>
+        <v>83071</v>
       </c>
       <c r="D112" t="n">
-        <v>60.32</v>
+        <v>-0.78</v>
       </c>
       <c r="E112" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F112" t="n">
-        <v>705</v>
+        <v>520</v>
       </c>
       <c r="G112" t="n">
-        <v>50.51</v>
+        <v>338.95</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>960</v>
+      </c>
+      <c r="L112" t="n">
+        <v>104</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.411</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:13.371</t>
+          <t>2026-05-29 09:41:37.974</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421995538</v>
+        <v>1780022496987</v>
       </c>
       <c r="C113" t="n">
-        <v>86851</v>
+        <v>83374</v>
       </c>
       <c r="D113" t="n">
-        <v>-18.69</v>
+        <v>302.25</v>
       </c>
       <c r="E113" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F113" t="n">
-        <v>705</v>
+        <v>520</v>
       </c>
       <c r="G113" t="n">
-        <v>50.51</v>
+        <v>338.95</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K113" t="n">
+        <v>986</v>
+      </c>
+      <c r="L113" t="n">
+        <v>110</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.601</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:13.599</t>
+          <t>2026-05-29 09:41:37.975</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421995739</v>
+        <v>1780022497187</v>
       </c>
       <c r="C114" t="n">
-        <v>87091</v>
+        <v>83896</v>
       </c>
       <c r="D114" t="n">
-        <v>222.24</v>
+        <v>809.14</v>
       </c>
       <c r="E114" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F114" t="n">
-        <v>705</v>
+        <v>520</v>
       </c>
       <c r="G114" t="n">
-        <v>50.51</v>
+        <v>338.95</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>787</v>
+      </c>
+      <c r="L114" t="n">
+        <v>109</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.592</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.038</t>
+          <t>2026-05-29 09:41:38.397</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421995941</v>
+        <v>1780022497387</v>
       </c>
       <c r="C115" t="n">
-        <v>87384</v>
+        <v>83087</v>
       </c>
       <c r="D115" t="n">
-        <v>504.13</v>
+        <v>-40.32</v>
       </c>
       <c r="E115" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F115" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G115" t="n">
-        <v>46.59</v>
+        <v>338.95</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1009</v>
+      </c>
+      <c r="L115" t="n">
+        <v>107</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.382</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.038</t>
+          <t>2026-05-29 09:41:38.399</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421996142</v>
+        <v>1780022497587</v>
       </c>
       <c r="C116" t="n">
-        <v>86578</v>
+        <v>83145</v>
       </c>
       <c r="D116" t="n">
-        <v>-327.08</v>
+        <v>19.7</v>
       </c>
       <c r="E116" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F116" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G116" t="n">
-        <v>46.59</v>
+        <v>338.95</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>811</v>
+      </c>
+      <c r="L116" t="n">
+        <v>107</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.468</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.426</t>
+          <t>2026-05-29 09:41:40.429</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421996343</v>
+        <v>1780022497806</v>
       </c>
       <c r="C117" t="n">
-        <v>86916</v>
+        <v>83300</v>
       </c>
       <c r="D117" t="n">
-        <v>27.28</v>
+        <v>173.72</v>
       </c>
       <c r="E117" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F117" t="n">
-        <v>765</v>
+        <v>2018</v>
       </c>
       <c r="G117" t="n">
-        <v>46.59</v>
+        <v>338.95</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K117" t="n">
+        <v>2621</v>
+      </c>
+      <c r="L117" t="n">
+        <v>114</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.202</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.427</t>
+          <t>2026-05-29 09:41:40.430</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421996545</v>
+        <v>1780022498006</v>
       </c>
       <c r="C118" t="n">
-        <v>87153</v>
+        <v>82898</v>
       </c>
       <c r="D118" t="n">
-        <v>262.91</v>
+        <v>-236.97</v>
       </c>
       <c r="E118" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F118" t="n">
-        <v>765</v>
+        <v>2018</v>
       </c>
       <c r="G118" t="n">
-        <v>46.59</v>
+        <v>338.95</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2423</v>
+      </c>
+      <c r="L118" t="n">
+        <v>108</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.093</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.846</t>
+          <t>2026-05-29 09:41:40.431</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421996746</v>
+        <v>1780022498206</v>
       </c>
       <c r="C119" t="n">
-        <v>87378</v>
+        <v>82311</v>
       </c>
       <c r="D119" t="n">
-        <v>474.77</v>
+        <v>-812.12</v>
       </c>
       <c r="E119" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F119" t="n">
-        <v>745</v>
+        <v>2018</v>
       </c>
       <c r="G119" t="n">
-        <v>45.68</v>
+        <v>338.95</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2224</v>
+      </c>
+      <c r="L119" t="n">
+        <v>108</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:14.847</t>
+          <t>2026-05-29 09:41:40.432</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421996948</v>
+        <v>1780022498406</v>
       </c>
       <c r="C120" t="n">
-        <v>86696</v>
+        <v>81997</v>
       </c>
       <c r="D120" t="n">
-        <v>-230.97</v>
+        <v>-1085.52</v>
       </c>
       <c r="E120" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F120" t="n">
-        <v>745</v>
+        <v>2018</v>
       </c>
       <c r="G120" t="n">
-        <v>45.68</v>
+        <v>338.95</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L120" t="n">
+        <v>112</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:15.394</t>
+          <t>2026-05-29 09:41:40.942</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421997149</v>
+        <v>1780022498606</v>
       </c>
       <c r="C121" t="n">
-        <v>87032</v>
+        <v>81838</v>
       </c>
       <c r="D121" t="n">
-        <v>116.58</v>
+        <v>-1190.24</v>
       </c>
       <c r="E121" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F121" t="n">
-        <v>745</v>
+        <v>2018</v>
       </c>
       <c r="G121" t="n">
-        <v>45.68</v>
+        <v>338.95</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2335</v>
+      </c>
+      <c r="L121" t="n">
+        <v>107</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:15.395</t>
+          <t>2026-05-29 09:41:40.943</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421997350</v>
+        <v>1780022498806</v>
       </c>
       <c r="C122" t="n">
-        <v>87374</v>
+        <v>81860</v>
       </c>
       <c r="D122" t="n">
-        <v>452.75</v>
+        <v>-1108.73</v>
       </c>
       <c r="E122" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F122" t="n">
-        <v>685</v>
+        <v>2018</v>
       </c>
       <c r="G122" t="n">
-        <v>35.02</v>
+        <v>338.95</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J122" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2136</v>
+      </c>
+      <c r="L122" t="n">
+        <v>119</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:15.395</t>
+          <t>2026-05-29 09:41:40.945</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421997552</v>
+        <v>1780022499006</v>
       </c>
       <c r="C123" t="n">
-        <v>86699</v>
+        <v>82074</v>
       </c>
       <c r="D123" t="n">
-        <v>-244.89</v>
+        <v>-839.29</v>
       </c>
       <c r="E123" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F123" t="n">
-        <v>685</v>
+        <v>2018</v>
       </c>
       <c r="G123" t="n">
-        <v>35.02</v>
+        <v>338.95</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J123" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1937</v>
+      </c>
+      <c r="L123" t="n">
+        <v>113</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.331</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:15.671</t>
+          <t>2026-05-29 09:41:42.202</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421997753</v>
+        <v>1780022499206</v>
       </c>
       <c r="C124" t="n">
-        <v>86910</v>
+        <v>82252</v>
       </c>
       <c r="D124" t="n">
-        <v>-21.64</v>
+        <v>-619.33</v>
       </c>
       <c r="E124" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F124" t="n">
-        <v>685</v>
+        <v>1400</v>
       </c>
       <c r="G124" t="n">
-        <v>35.02</v>
+        <v>374.48</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J124" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2995</v>
+      </c>
+      <c r="L124" t="n">
+        <v>107</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:16.087</t>
+          <t>2026-05-29 09:41:42.203</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421997955</v>
+        <v>1780022500045</v>
       </c>
       <c r="C125" t="n">
-        <v>87030</v>
+        <v>81678</v>
       </c>
       <c r="D125" t="n">
-        <v>99.44</v>
+        <v>-1162.36</v>
       </c>
       <c r="E125" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F125" t="n">
-        <v>685</v>
+        <v>1400</v>
       </c>
       <c r="G125" t="n">
-        <v>35.02</v>
+        <v>374.48</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>66.39</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2158</v>
+      </c>
+      <c r="L125" t="n">
+        <v>116</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.573</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:16.087</t>
+          <t>2026-05-29 09:41:42.205</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421998156</v>
+        <v>1780022500245</v>
       </c>
       <c r="C126" t="n">
-        <v>87353</v>
+        <v>82447</v>
       </c>
       <c r="D126" t="n">
-        <v>417.47</v>
+        <v>-335.24</v>
       </c>
       <c r="E126" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F126" t="n">
-        <v>806</v>
+        <v>1400</v>
       </c>
       <c r="G126" t="n">
-        <v>42.38</v>
+        <v>374.48</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1959</v>
+      </c>
+      <c r="L126" t="n">
+        <v>121</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.016</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:16.465</t>
+          <t>2026-05-29 09:41:42.211</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421998358</v>
+        <v>1780022500445</v>
       </c>
       <c r="C127" t="n">
-        <v>86538</v>
+        <v>82079</v>
       </c>
       <c r="D127" t="n">
-        <v>-418.41</v>
+        <v>-686.48</v>
       </c>
       <c r="E127" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F127" t="n">
-        <v>806</v>
+        <v>1159</v>
       </c>
       <c r="G127" t="n">
-        <v>42.38</v>
+        <v>378.8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1765</v>
+      </c>
+      <c r="L127" t="n">
+        <v>119</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.004</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:16.466</t>
+          <t>2026-05-29 09:41:42.779</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421998559</v>
+        <v>1780022500646</v>
       </c>
       <c r="C128" t="n">
-        <v>86854</v>
+        <v>82291</v>
       </c>
       <c r="D128" t="n">
-        <v>-81.48999999999999</v>
+        <v>-440.16</v>
       </c>
       <c r="E128" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F128" t="n">
-        <v>806</v>
+        <v>1159</v>
       </c>
       <c r="G128" t="n">
-        <v>42.38</v>
+        <v>378.8</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2132</v>
+      </c>
+      <c r="L128" t="n">
+        <v>106</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.537</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:17.001</t>
+          <t>2026-05-29 09:41:42.780</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421998760</v>
+        <v>1780022500864</v>
       </c>
       <c r="C129" t="n">
-        <v>87131</v>
+        <v>81154</v>
       </c>
       <c r="D129" t="n">
-        <v>199.59</v>
+        <v>-1555.15</v>
       </c>
       <c r="E129" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F129" t="n">
-        <v>806</v>
+        <v>1159</v>
       </c>
       <c r="G129" t="n">
-        <v>42.38</v>
+        <v>378.8</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1915</v>
+      </c>
+      <c r="L129" t="n">
+        <v>120</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:17.002</t>
+          <t>2026-05-29 09:41:42.781</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421998962</v>
+        <v>1780022501064</v>
       </c>
       <c r="C130" t="n">
-        <v>87493</v>
+        <v>80952</v>
       </c>
       <c r="D130" t="n">
-        <v>551.61</v>
+        <v>-1679.39</v>
       </c>
       <c r="E130" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F130" t="n">
-        <v>725</v>
+        <v>1159</v>
       </c>
       <c r="G130" t="n">
-        <v>39.99</v>
+        <v>378.8</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1716</v>
+      </c>
+      <c r="L130" t="n">
+        <v>111</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.972</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:17.002</t>
+          <t>2026-05-29 09:41:42.782</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421999163</v>
+        <v>1780022501264</v>
       </c>
       <c r="C131" t="n">
-        <v>86762</v>
+        <v>81576</v>
       </c>
       <c r="D131" t="n">
-        <v>-206.97</v>
+        <v>-971.42</v>
       </c>
       <c r="E131" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F131" t="n">
-        <v>725</v>
+        <v>1159</v>
       </c>
       <c r="G131" t="n">
-        <v>39.99</v>
+        <v>378.8</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1518</v>
+      </c>
+      <c r="L131" t="n">
+        <v>112</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.833</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:17.287</t>
+          <t>2026-05-29 09:41:42.783</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421999365</v>
+        <v>1780022501464</v>
       </c>
       <c r="C132" t="n">
-        <v>87190</v>
+        <v>82095</v>
       </c>
       <c r="D132" t="n">
-        <v>231.38</v>
+        <v>-403.85</v>
       </c>
       <c r="E132" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F132" t="n">
-        <v>725</v>
+        <v>1159</v>
       </c>
       <c r="G132" t="n">
-        <v>39.99</v>
+        <v>378.8</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1319</v>
+      </c>
+      <c r="L132" t="n">
+        <v>113</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.505</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:17.287</t>
+          <t>2026-05-29 09:41:43.238</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421999566</v>
+        <v>1780022501664</v>
       </c>
       <c r="C133" t="n">
-        <v>87346</v>
+        <v>81551</v>
       </c>
       <c r="D133" t="n">
-        <v>375.81</v>
+        <v>-927.66</v>
       </c>
       <c r="E133" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F133" t="n">
-        <v>725</v>
+        <v>1159</v>
       </c>
       <c r="G133" t="n">
-        <v>39.99</v>
+        <v>378.8</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:17.712</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1779421999767</v>
-      </c>
-      <c r="C134" t="n">
-        <v>87602</v>
-      </c>
-      <c r="D134" t="n">
-        <v>613.02</v>
-      </c>
-      <c r="E134" t="n">
-        <v>81</v>
-      </c>
-      <c r="F134" t="n">
-        <v>725</v>
-      </c>
-      <c r="G134" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:17.713</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1779421999969</v>
-      </c>
-      <c r="C135" t="n">
-        <v>86838</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-181.63</v>
-      </c>
-      <c r="E135" t="n">
-        <v>81</v>
-      </c>
-      <c r="F135" t="n">
-        <v>725</v>
-      </c>
-      <c r="G135" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.106</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1779422000170</v>
-      </c>
-      <c r="C136" t="n">
-        <v>87042</v>
-      </c>
-      <c r="D136" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="E136" t="n">
-        <v>81</v>
-      </c>
-      <c r="F136" t="n">
-        <v>725</v>
-      </c>
-      <c r="G136" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.107</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1779422000372</v>
-      </c>
-      <c r="C137" t="n">
-        <v>87253</v>
-      </c>
-      <c r="D137" t="n">
-        <v>240.88</v>
-      </c>
-      <c r="E137" t="n">
-        <v>81</v>
-      </c>
-      <c r="F137" t="n">
-        <v>725</v>
-      </c>
-      <c r="G137" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.527</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1779422000573</v>
-      </c>
-      <c r="C138" t="n">
-        <v>87589</v>
-      </c>
-      <c r="D138" t="n">
-        <v>564.83</v>
-      </c>
-      <c r="E138" t="n">
-        <v>75</v>
-      </c>
-      <c r="F138" t="n">
-        <v>947</v>
-      </c>
-      <c r="G138" t="n">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.527</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1779422000774</v>
-      </c>
-      <c r="C139" t="n">
-        <v>86839</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-213.41</v>
-      </c>
-      <c r="E139" t="n">
-        <v>75</v>
-      </c>
-      <c r="F139" t="n">
-        <v>947</v>
-      </c>
-      <c r="G139" t="n">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.983</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779422000976</v>
-      </c>
-      <c r="C140" t="n">
-        <v>87119</v>
-      </c>
-      <c r="D140" t="n">
-        <v>77.26000000000001</v>
-      </c>
-      <c r="E140" t="n">
-        <v>75</v>
-      </c>
-      <c r="F140" t="n">
-        <v>947</v>
-      </c>
-      <c r="G140" t="n">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:18.990</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779422001177</v>
-      </c>
-      <c r="C141" t="n">
-        <v>87393</v>
-      </c>
-      <c r="D141" t="n">
-        <v>347.4</v>
-      </c>
-      <c r="E141" t="n">
-        <v>75</v>
-      </c>
-      <c r="F141" t="n">
-        <v>947</v>
-      </c>
-      <c r="G141" t="n">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:19.562</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779422001379</v>
-      </c>
-      <c r="C142" t="n">
-        <v>87759</v>
-      </c>
-      <c r="D142" t="n">
-        <v>696.03</v>
-      </c>
-      <c r="E142" t="n">
-        <v>76</v>
-      </c>
-      <c r="F142" t="n">
-        <v>745</v>
-      </c>
-      <c r="G142" t="n">
-        <v>79.53</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:19.562</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779422001580</v>
-      </c>
-      <c r="C143" t="n">
-        <v>86975</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-122.77</v>
-      </c>
-      <c r="E143" t="n">
-        <v>76</v>
-      </c>
-      <c r="F143" t="n">
-        <v>745</v>
-      </c>
-      <c r="G143" t="n">
-        <v>79.53</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:19.563</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779422001781</v>
-      </c>
-      <c r="C144" t="n">
-        <v>87290</v>
-      </c>
-      <c r="D144" t="n">
-        <v>198.37</v>
-      </c>
-      <c r="E144" t="n">
-        <v>76</v>
-      </c>
-      <c r="F144" t="n">
-        <v>745</v>
-      </c>
-      <c r="G144" t="n">
-        <v>79.53</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:19.960</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779422001983</v>
-      </c>
-      <c r="C145" t="n">
-        <v>87466</v>
-      </c>
-      <c r="D145" t="n">
-        <v>364.45</v>
-      </c>
-      <c r="E145" t="n">
-        <v>76</v>
-      </c>
-      <c r="F145" t="n">
-        <v>725</v>
-      </c>
-      <c r="G145" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:19.961</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779422002184</v>
-      </c>
-      <c r="C146" t="n">
-        <v>87752</v>
-      </c>
-      <c r="D146" t="n">
-        <v>632.22</v>
-      </c>
-      <c r="E146" t="n">
-        <v>76</v>
-      </c>
-      <c r="F146" t="n">
-        <v>725</v>
-      </c>
-      <c r="G146" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:20.380</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779422002386</v>
-      </c>
-      <c r="C147" t="n">
-        <v>86986</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-165.39</v>
-      </c>
-      <c r="E147" t="n">
-        <v>76</v>
-      </c>
-      <c r="F147" t="n">
-        <v>725</v>
-      </c>
-      <c r="G147" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:20.381</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779422002587</v>
-      </c>
-      <c r="C148" t="n">
-        <v>87308</v>
-      </c>
-      <c r="D148" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="E148" t="n">
-        <v>76</v>
-      </c>
-      <c r="F148" t="n">
-        <v>725</v>
-      </c>
-      <c r="G148" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.204</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779422002788</v>
-      </c>
-      <c r="C149" t="n">
-        <v>87659</v>
-      </c>
-      <c r="D149" t="n">
-        <v>507.64</v>
-      </c>
-      <c r="E149" t="n">
-        <v>75</v>
-      </c>
-      <c r="F149" t="n">
-        <v>785</v>
-      </c>
-      <c r="G149" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.236</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779422002990</v>
-      </c>
-      <c r="C150" t="n">
-        <v>87810</v>
-      </c>
-      <c r="D150" t="n">
-        <v>633.26</v>
-      </c>
-      <c r="E150" t="n">
-        <v>75</v>
-      </c>
-      <c r="F150" t="n">
-        <v>785</v>
-      </c>
-      <c r="G150" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.237</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779422003191</v>
-      </c>
-      <c r="C151" t="n">
-        <v>87097</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-111.41</v>
-      </c>
-      <c r="E151" t="n">
-        <v>75</v>
-      </c>
-      <c r="F151" t="n">
-        <v>785</v>
-      </c>
-      <c r="G151" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.238</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779422003393</v>
-      </c>
-      <c r="C152" t="n">
-        <v>87377</v>
-      </c>
-      <c r="D152" t="n">
-        <v>174.16</v>
-      </c>
-      <c r="E152" t="n">
-        <v>75</v>
-      </c>
-      <c r="F152" t="n">
-        <v>785</v>
-      </c>
-      <c r="G152" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.585</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779422003594</v>
-      </c>
-      <c r="C153" t="n">
-        <v>87727</v>
-      </c>
-      <c r="D153" t="n">
-        <v>515.46</v>
-      </c>
-      <c r="E153" t="n">
-        <v>78</v>
-      </c>
-      <c r="F153" t="n">
-        <v>806</v>
-      </c>
-      <c r="G153" t="n">
-        <v>73.55</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:21.586</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1779422003796</v>
-      </c>
-      <c r="C154" t="n">
-        <v>87878</v>
-      </c>
-      <c r="D154" t="n">
-        <v>640.6799999999999</v>
-      </c>
-      <c r="E154" t="n">
-        <v>78</v>
-      </c>
-      <c r="F154" t="n">
-        <v>806</v>
-      </c>
-      <c r="G154" t="n">
-        <v>73.55</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:22.023</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1779422003997</v>
-      </c>
-      <c r="C155" t="n">
-        <v>87153</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-116.35</v>
-      </c>
-      <c r="E155" t="n">
-        <v>78</v>
-      </c>
-      <c r="F155" t="n">
-        <v>806</v>
-      </c>
-      <c r="G155" t="n">
-        <v>73.55</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I133" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J133" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1573</v>
+      </c>
+      <c r="L133" t="n">
+        <v>115</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.829</v>
       </c>
     </row>
   </sheetData>
